--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:28</t>
+    <t xml:space="preserve">2026-09-09 23:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:25</t>
+    <t xml:space="preserve">2026-09-17 14:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2022_valparaiso.xlsx
@@ -90,12 +90,12 @@
     <t xml:space="preserve">Villa Alemana</t>
   </si>
   <si>
+    <t xml:space="preserve">Zapallar</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Antonio</t>
   </si>
   <si>
-    <t xml:space="preserve">Zapallar</t>
-  </si>
-  <si>
     <t xml:space="preserve">Llaillay</t>
   </si>
   <si>
@@ -117,12 +117,12 @@
     <t xml:space="preserve">Quintero</t>
   </si>
   <si>
+    <t xml:space="preserve">San Esteban</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nogales</t>
   </si>
   <si>
-    <t xml:space="preserve">San Esteban</t>
-  </si>
-  <si>
     <t xml:space="preserve">Casablanca</t>
   </si>
   <si>
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:20</t>
+    <t xml:space="preserve">2026-09-23 12:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -909,7 +909,7 @@
         <v>24</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>5601</v>
+        <v>5405</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2022</v>
@@ -926,7 +926,7 @@
         <v>25</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>5405</v>
+        <v>5601</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2022</v>
@@ -1062,7 +1062,7 @@
         <v>33</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>5506</v>
+        <v>5304</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2022</v>
@@ -1079,7 +1079,7 @@
         <v>34</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>5304</v>
+        <v>5506</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>2022</v>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2022_valparaiso.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t xml:space="preserve">Región</t>
   </si>
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:48</t>
+    <t xml:space="preserve">2026-10-01 23:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -174,7 +174,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingreso sobre la mediana nacional (%)</t>
+    <t xml:space="preserve">% bajo 50% de la mediana</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
@@ -187,9 +187,6 @@
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% sobre mediana</t>
   </si>
 </sst>
 </file>
@@ -1301,7 +1298,7 @@
         <v>56</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:08</t>
+    <t xml:space="preserve">2026-10-02 11:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 11:20</t>
+    <t xml:space="preserve">2026-10-02 15:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:06</t>
+    <t xml:space="preserve">2026-10-04 09:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:24</t>
+    <t xml:space="preserve">2026-10-05 12:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
